--- a/dashboard/leitura/Parcial_Piracicaba.xlsx
+++ b/dashboard/leitura/Parcial_Piracicaba.xlsx
@@ -532,299 +532,299 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>HENRIQUE DOS SANTOS DIAS</t>
+          <t>SIDNEY CAMARGO</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>496</v>
+        <v>1</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>496</v>
+        <v>1</v>
       </c>
       <c r="E3" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>JOSE LUIS CALIXTO DA SILVA</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="2" t="n">
         <v>122</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>122</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>0</v>
+      <c r="C4" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>54.1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>SIDNEY CAMARGO</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>0</v>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>FRANCISCO PIO SANTOS</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>213</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>79.81</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>ROBSON RICARDO GUILHERME</t>
+          <t>BRUNA RODRIGUES DE LIMA E SILV</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>207</v>
+        <v>645</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>90</v>
+        <v>562</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>43.48</v>
+        <v>87.13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>BRUNA RODRIGUES DE LIMA E SILV</t>
+          <t>MARCELO DO PRADO CAMARGO</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>645</v>
+        <v>198</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>302</v>
+        <v>175</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>343</v>
+        <v>23</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>46.82</v>
+        <v>88.38</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO PIO SANTOS</t>
+          <t>ALEX JONYRIGO</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>213</v>
+        <v>318</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>104</v>
+        <v>301</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>109</v>
+        <v>17</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>48.83</v>
+        <v>94.65000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>ALEX JONYRIGO</t>
+          <t>HENRIQUE DOS SANTOS DIAS</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>318</v>
+        <v>496</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>175</v>
+        <v>478</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>143</v>
+        <v>18</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>55.03</v>
+        <v>96.37</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>EDIRLEI LUIS CARNELUTTI</t>
+          <t>ADAO RIBEIRO</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>554</v>
+        <v>80</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>323</v>
+        <v>78</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>231</v>
+        <v>2</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>58.3</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>ROGERIO BENEDITO DE SOUZA</t>
+          <t>ROBSON RICARDO GUILHERME</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>422</v>
+        <v>209</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>263</v>
+        <v>207</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>159</v>
+        <v>2</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>62.32</v>
+        <v>99.04000000000001</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>OSVANDIR PINTO DA SILVA</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>619</v>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>477</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>142</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>77.06</v>
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>EDIRLEI LUIS CARNELUTTI</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>554</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>554</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>MARCELO DO PRADO CAMARGO</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>198</v>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>153</v>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>77.27</v>
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>ALESSANDRO NERES DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>414</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>414</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>LUCAS CARDOSO RESERVA</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n">
+      <c r="B14" s="6" t="n">
         <v>255</v>
       </c>
-      <c r="C14" s="2" t="n">
-        <v>202</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>79.22</v>
+      <c r="C14" s="6" t="n">
+        <v>255</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>ADAO RIBEIRO</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>72</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>90</v>
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>MAURO FERNANDO MANTUAN</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>ALESSANDRO JOSE CASSIMIRRO</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n">
+      <c r="B16" s="6" t="n">
         <v>251</v>
       </c>
-      <c r="C16" s="2" t="n">
-        <v>227</v>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>90.44</v>
+      <c r="C16" s="6" t="n">
+        <v>251</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>RENAN DE CARVALHO OLIVEIRA</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>365</v>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>346</v>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="E17" s="5" t="n">
-        <v>94.79000000000001</v>
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>JAIME JOSE CIPRIANO</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>MAURO FERNANDO MANTUAN</t>
+          <t>RENAN DE CARVALHO OLIVEIRA</t>
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>2</v>
+        <v>365</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>2</v>
+        <v>365</v>
       </c>
       <c r="D18" s="6" t="n">
         <v>0</v>
@@ -836,14 +836,14 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>JAIME JOSE CIPRIANO</t>
+          <t>OSVANDIR PINTO DA SILVA</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>65</v>
+        <v>619</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>65</v>
+        <v>619</v>
       </c>
       <c r="D19" s="6" t="n">
         <v>0</v>
@@ -855,14 +855,14 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>ALESSANDRO NERES DOS SANTOS</t>
+          <t>ROGERIO BENEDITO DE SOUZA</t>
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="D20" s="6" t="n">
         <v>0</v>

--- a/dashboard/leitura/Parcial_Piracicaba.xlsx
+++ b/dashboard/leitura/Parcial_Piracicaba.xlsx
@@ -608,77 +608,77 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>MARCELO DO PRADO CAMARGO</t>
+          <t>ALEX JONYRIGO</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>198</v>
+        <v>318</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>175</v>
+        <v>301</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>88.38</v>
+        <v>94.65000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ALEX JONYRIGO</t>
+          <t>HENRIQUE DOS SANTOS DIAS</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>318</v>
+        <v>496</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>301</v>
+        <v>478</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>94.65000000000001</v>
+        <v>96.37</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>HENRIQUE DOS SANTOS DIAS</t>
+          <t>ADAO RIBEIRO</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>496</v>
+        <v>80</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>478</v>
+        <v>78</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>96.37</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>ADAO RIBEIRO</t>
+          <t>MARCELO DO PRADO CAMARGO</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>78</v>
+        <v>195</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>97.5</v>
+        <v>98.48</v>
       </c>
     </row>
     <row r="11">

--- a/dashboard/leitura/Parcial_Piracicaba.xlsx
+++ b/dashboard/leitura/Parcial_Piracicaba.xlsx
@@ -558,13 +558,13 @@
         <v>122</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>54.1</v>
+        <v>68.03</v>
       </c>
     </row>
     <row r="5">
@@ -596,13 +596,13 @@
         <v>645</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>562</v>
+        <v>593</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>87.13</v>
+        <v>91.94</v>
       </c>
     </row>
     <row r="7">
@@ -627,77 +627,77 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>HENRIQUE DOS SANTOS DIAS</t>
+          <t>ADAO RIBEIRO</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>496</v>
+        <v>80</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>478</v>
+        <v>78</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>96.37</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>ADAO RIBEIRO</t>
+          <t>MARCELO DO PRADO CAMARGO</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>78</v>
+        <v>196</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>97.5</v>
+        <v>98.98999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>MARCELO DO PRADO CAMARGO</t>
+          <t>ROBSON RICARDO GUILHERME</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>98.48</v>
+        <v>99.04000000000001</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>ROBSON RICARDO GUILHERME</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>209</v>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>207</v>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>99.04000000000001</v>
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>ALESSANDRO NERES DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>414</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>414</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -722,14 +722,14 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>ALESSANDRO NERES DOS SANTOS</t>
+          <t>HENRIQUE DOS SANTOS DIAS</t>
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>414</v>
+        <v>496</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>414</v>
+        <v>496</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>0</v>
@@ -779,14 +779,14 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>ALESSANDRO JOSE CASSIMIRRO</t>
+          <t>JAIME JOSE CIPRIANO</t>
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>251</v>
+        <v>65</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>251</v>
+        <v>65</v>
       </c>
       <c r="D16" s="6" t="n">
         <v>0</v>
@@ -798,14 +798,14 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>JAIME JOSE CIPRIANO</t>
+          <t>ALESSANDRO JOSE CASSIMIRRO</t>
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>65</v>
+        <v>251</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>65</v>
+        <v>251</v>
       </c>
       <c r="D17" s="6" t="n">
         <v>0</v>

--- a/dashboard/leitura/Parcial_Piracicaba.xlsx
+++ b/dashboard/leitura/Parcial_Piracicaba.xlsx
@@ -577,13 +577,13 @@
         <v>213</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>79.81</v>
+        <v>80.28</v>
       </c>
     </row>
     <row r="6">
